--- a/PIMTC_GoogleSheets_Import.xlsx
+++ b/PIMTC_GoogleSheets_Import.xlsx
@@ -16,6 +16,9 @@
     <sheet name="Standings" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Playoffs" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Results" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Live" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Updates" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="LiveStandings" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="159">
   <si>
     <t xml:space="preserve">rank</t>
   </si>
@@ -396,6 +399,114 @@
   </si>
   <si>
     <t xml:space="preserve">5-player round robin completed. Mauliza Arsita finished 1st (4-0), followed by Azwarni Islamiah, Noviana Putri, Fierda, and Lisa Zulmayeti.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">startDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pimtc500-doubles-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turnamen Tenis Ganda Pria PIMTC 500 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ongoing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIM Tennis Arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">July 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7pt at 6-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A random pairs-draw men's doubles tournament. 8 pairs split into Group A and Group B for round-robin group stage play, best of 1 set to 7 games with a 7-point tiebreak at 6-6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Stage Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random pairs draw complete — 8 pairs split into Group A and Group B for round-robin group play. First results are in from Group B: Fariz/Dian opened with a 7-3 win over Memed/Heri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gipa / Mursal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatur / Dian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osman / Ferdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arief / Moeda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fariz / Dian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memed / Heri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akbar / Syahrul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zes / Rahmat</t>
   </si>
 </sst>
 </file>
@@ -485,7 +596,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -496,6 +607,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1139,6 +1254,412 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="5" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -2620,4 +3141,99 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="55"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/PIMTC_GoogleSheets_Import.xlsx
+++ b/PIMTC_GoogleSheets_Import.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Live" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Updates" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="LiveStandings" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Schedule" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="182">
   <si>
     <t xml:space="preserve">rank</t>
   </si>
@@ -507,6 +508,75 @@
   </si>
   <si>
     <t xml:space="preserve">Zes / Rahmat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapangan 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fariz/Dian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akbar/Syahrul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gipa/Mursal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dian/Fatur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapangan 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arief/Moeda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osman/Ferdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rabu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heri/Memed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zes/Rahmat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syahrul/Akbar</t>
   </si>
 </sst>
 </file>
@@ -1660,6 +1730,191 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D9" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -1854,15 +2109,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1876,15 +2131,18 @@
         <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1898,16 +2156,17 @@
       <c r="C2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>5.217773</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>97.029371</v>
       </c>
     </row>

--- a/PIMTC_GoogleSheets_Import.xlsx
+++ b/PIMTC_GoogleSheets_Import.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Updates" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="LiveStandings" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Schedule" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Gallery" sheetId="13" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="185">
   <si>
     <t xml:space="preserve">rank</t>
   </si>
@@ -204,6 +205,9 @@
     <t xml:space="preserve">about</t>
   </si>
   <si>
+    <t xml:space="preserve">mediaType</t>
+  </si>
+  <si>
     <t xml:space="preserve">instagram</t>
   </si>
   <si>
@@ -225,6 +229,9 @@
     <t xml:space="preserve">PIM Tennis Club is a community-based sports club located in Pupuk Iskandar Muda. We host regular training sessions, tournaments, and represent our organization in external events. Whether you're new to the sport or looking to sharpen your game, our club welcomes players of all levels.</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.instagram.com/reel/DGKAtoVh2eO/?igsh=MXFhZWY2dmlpaXJqcQ==</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.instagram.com/pimtennisclub/</t>
   </si>
   <si>
@@ -577,6 +584,9 @@
   </si>
   <si>
     <t xml:space="preserve">Syahrul/Akbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event</t>
   </si>
 </sst>
 </file>
@@ -1342,39 +1352,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1406,51 +1416,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>0</v>
@@ -1476,16 +1486,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>0</v>
@@ -1511,16 +1521,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>0</v>
@@ -1546,16 +1556,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>0</v>
@@ -1581,16 +1591,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>1</v>
@@ -1616,16 +1626,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>1</v>
@@ -1651,16 +1661,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>0</v>
@@ -1686,16 +1696,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>0</v>
@@ -1746,162 +1756,205 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="E5" s="0" t="s">
         <v>173</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="E6" s="0" t="s">
         <v>176</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>170</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>179</v>
+        <v>181</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2109,15 +2162,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2145,28 +2200,36 @@
       <c r="H1" s="1" t="s">
         <v>60</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="E2" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G2" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="2" t="n">
         <v>5.217773</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>97.029371</v>
       </c>
     </row>
@@ -2197,100 +2260,100 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2319,24 +2382,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>14</v>
@@ -2348,12 +2411,12 @@
         <v>6</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>5</v>
@@ -2397,45 +2460,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>1</v>
@@ -2453,24 +2516,24 @@
         <v>18</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G3" s="0" t="n">
         <v>6</v>
@@ -2482,18 +2545,18 @@
         <v>14</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>3</v>
@@ -2511,18 +2574,18 @@
         <v>14</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>4</v>
@@ -2540,24 +2603,24 @@
         <v>12</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G6" s="0" t="n">
         <v>6</v>
@@ -2569,18 +2632,18 @@
         <v>10</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>6</v>
@@ -2598,18 +2661,18 @@
         <v>8</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>7</v>
@@ -2627,18 +2690,18 @@
         <v>8</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>1</v>
@@ -2656,18 +2719,18 @@
         <v>16</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>2</v>
@@ -2685,18 +2748,18 @@
         <v>16</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>3</v>
@@ -2714,18 +2777,18 @@
         <v>14</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>4</v>
@@ -2743,18 +2806,18 @@
         <v>12</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>5</v>
@@ -2772,18 +2835,18 @@
         <v>12</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>6</v>
@@ -2801,18 +2864,18 @@
         <v>8</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>7</v>
@@ -2830,18 +2893,18 @@
         <v>6</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>1</v>
@@ -2859,18 +2922,18 @@
         <v>6</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>2</v>
@@ -2888,18 +2951,18 @@
         <v>4</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>3</v>
@@ -2917,18 +2980,18 @@
         <v>4</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>4</v>
@@ -2946,18 +3009,18 @@
         <v>2</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>1</v>
@@ -2975,18 +3038,18 @@
         <v>6</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>2</v>
@@ -3004,24 +3067,24 @@
         <v>6</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G22" s="0" t="n">
         <v>2</v>
@@ -3033,18 +3096,18 @@
         <v>2</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>4</v>
@@ -3062,15 +3125,15 @@
         <v>2</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>1</v>
@@ -3079,7 +3142,7 @@
         <v>42</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G24" s="0" t="n">
         <v>4</v>
@@ -3093,10 +3156,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>2</v>
@@ -3105,7 +3168,7 @@
         <v>45</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G25" s="0" t="n">
         <v>4</v>
@@ -3119,10 +3182,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>3</v>
@@ -3131,7 +3194,7 @@
         <v>48</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G26" s="0" t="n">
         <v>4</v>
@@ -3145,10 +3208,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>4</v>
@@ -3157,7 +3220,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G27" s="0" t="n">
         <v>4</v>
@@ -3171,10 +3234,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>5</v>
@@ -3183,7 +3246,7 @@
         <v>52</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G28" s="0" t="n">
         <v>4</v>
@@ -3223,30 +3286,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>9</v>
@@ -3255,7 +3318,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F2" s="0" t="s">
         <v>9</v>
@@ -3263,10 +3326,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>13</v>
@@ -3275,7 +3338,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>13</v>
@@ -3283,10 +3346,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>9</v>
@@ -3295,7 +3358,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F4" s="0" t="s">
         <v>9</v>
@@ -3327,68 +3390,68 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3424,51 +3487,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>8</v>
@@ -3480,10 +3543,10 @@
         <v>7</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/PIMTC_GoogleSheets_Import.xlsx
+++ b/PIMTC_GoogleSheets_Import.xlsx
@@ -21,6 +21,7 @@
     <sheet name="LiveStandings" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="Schedule" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Gallery" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="HomeGallery" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="187">
   <si>
     <t xml:space="preserve">rank</t>
   </si>
@@ -229,364 +230,370 @@
     <t xml:space="preserve">PIM Tennis Club is a community-based sports club located in Pupuk Iskandar Muda. We host regular training sessions, tournaments, and represent our organization in external events. Whether you're new to the sport or looking to sharpen your game, our club welcomes players of all levels.</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.instagram.com/pimtennisclub/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maps-api-ssl.google.com/maps?hl=en-US&amp;ll=5.2179,97.029367&amp;output=embed&amp;q=5.217773,97.029371&amp;z=17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roundOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roundName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">point</t>
+  </si>
+  <si>
+    <t xml:space="preserve">men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Features 2 groups (Group A and Group B), each with 7 players randomly assigned.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The top 4 players from each group advance to Round 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Players ranked 5th and below are eliminated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Features 2 groups of 4 players each, assigned through a cross-group system: Group A gets 1st &amp; 3rd from Group A, 2nd &amp; 4th from Group B; Group B gets 1st &amp; 3rd from Group B, 2nd &amp; 4th from Group A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Players from the same Round 1 group won't face each other again to avoid rematches.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The top 2 players from each group advance to the Semifinals.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">games</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tiebreak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7pt at 5-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">women</t>
+  </si>
+  <si>
+    <t xml:space="preserve">round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ranking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nickname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w</t>
+  </si>
+  <si>
+    <t xml:space="preserve">points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qualified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hafizh Furqan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zulfajri Ery S.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FALSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round Robin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pipi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">winner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semifinal 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semifinal 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group A and Group B pool play completed. Top 4 advanced from each group: Mansurni, Hafizh Furqan, Giffari Almuzani and Fariz Ridha from Group A; Aulia Moeda, Osman Saftari, Mursal Rajab and Arief Rahman from Group B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross-group stage completed. Top 2 from each group advanced to the Semifinals: Mansurni and Osman Saftari from Group A; Aulia Moeda and Mursal Rajab from Group B.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semifinals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mansurni defeated Mursal Rajab 6-2. Aulia Moeda defeated Osman Saftari 6-2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mansurni defeated Aulia Moeda 6-3 to win the championship.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-player round robin completed. Mauliza Arsita finished 1st (4-0), followed by Azwarni Islamiah, Noviana Putri, Fierda, and Lisa Zulmayeti.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">startDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pimtc500-doubles-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turnamen Tenis Ganda Pria PIMTC 500 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ongoing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIM Tennis Arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">July 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7pt at 6-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A random pairs-draw men's doubles tournament. 8 pairs split into Group A and Group B for round-robin group stage play, best of 1 set to 7 games with a 7-point tiebreak at 6-6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Stage Draw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random pairs draw complete — 8 pairs split into Group A and Group B for round-robin group play. First results are in from Group B: Fariz/Dian opened with a 7-3 win over Memed/Heri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gipa / Mursal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatur / Dian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osman / Ferdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arief / Moeda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fariz / Dian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Memed / Heri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akbar / Syahrul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zes / Rahmat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">court</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">team2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapangan 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fariz/Dian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akbar/Syahrul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gipa/Mursal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dian/Fatur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapangan 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arief/Moeda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Osman/Ferdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selasa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rabu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heri/Memed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zes/Rahmat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syahrul/Akbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Club Highlights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIMTC on the court.</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.instagram.com/reel/DGKAtoVh2eO/?igsh=MXFhZWY2dmlpaXJqcQ==</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.instagram.com/pimtennisclub/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://maps-api-ssl.google.com/maps?hl=en-US&amp;ll=5.2179,97.029367&amp;output=embed&amp;q=5.217773,97.029371&amp;z=17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roundOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">roundName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">point</t>
-  </si>
-  <si>
-    <t xml:space="preserve">men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Round 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Features 2 groups (Group A and Group B), each with 7 players randomly assigned.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The top 4 players from each group advance to Round 2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Players ranked 5th and below are eliminated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Round 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Features 2 groups of 4 players each, assigned through a cross-group system: Group A gets 1st &amp; 3rd from Group A, 2nd &amp; 4th from Group B; Group B gets 1st &amp; 3rd from Group B, 2nd &amp; 4th from Group A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Players from the same Round 1 group won't face each other again to avoid rematches.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The top 2 players from each group advance to the Semifinals.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">players</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">games</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tiebreak</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7pt at 5-5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">women</t>
-  </si>
-  <si>
-    <t xml:space="preserve">round</t>
-  </si>
-  <si>
-    <t xml:space="preserve">group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ranking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nickname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w</t>
-  </si>
-  <si>
-    <t xml:space="preserve">points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qualified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hafizh Furqan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zulfajri Ery S.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FALSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Round Robin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dekta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Novi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pipi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">winner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semifinal 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semifinal 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group A and Group B pool play completed. Top 4 advanced from each group: Mansurni, Hafizh Furqan, Giffari Almuzani and Fariz Ridha from Group A; Aulia Moeda, Osman Saftari, Mursal Rajab and Arief Rahman from Group B.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cross-group stage completed. Top 2 from each group advanced to the Semifinals: Mansurni and Osman Saftari from Group A; Aulia Moeda and Mursal Rajab from Group B.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semifinals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mansurni defeated Mursal Rajab 6-2. Aulia Moeda defeated Osman Saftari 6-2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mansurni defeated Aulia Moeda 6-3 to win the championship.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-player round robin completed. Mauliza Arsita finished 1st (4-0), followed by Azwarni Islamiah, Noviana Putri, Fierda, and Lisa Zulmayeti.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">startDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">teams</t>
-  </si>
-  <si>
-    <t xml:space="preserve">description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pimtc500-doubles-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turnamen Tenis Ganda Pria PIMTC 500 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ongoing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIM Tennis Arena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">July 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7pt at 6-6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A random pairs-draw men's doubles tournament. 8 pairs split into Group A and Group B for round-robin group stage play, best of 1 set to 7 games with a 7-point tiebreak at 6-6.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">order</t>
-  </si>
-  <si>
-    <t xml:space="preserve">caption</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Stage Draw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random pairs draw complete — 8 pairs split into Group A and Group B for round-robin group play. First results are in from Group B: Fariz/Dian opened with a 7-3 win over Memed/Heri.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pair</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Group Stage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gipa / Mursal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fatur / Dian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osman / Ferdy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arief / Moeda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fariz / Dian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Memed / Heri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akbar / Syahrul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zes / Rahmat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">court</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">team2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lapangan 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fariz/Dian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akbar/Syahrul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gipa/Mursal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dian/Fatur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lapangan 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arief/Moeda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osman/Ferdy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selasa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rabu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heri/Memed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zes/Rahmat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Syahrul/Akbar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">event</t>
   </si>
 </sst>
 </file>
@@ -1352,39 +1359,39 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1416,51 +1423,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E2" s="0" t="n">
         <v>0</v>
@@ -1486,16 +1493,16 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3" s="0" t="n">
         <v>0</v>
@@ -1521,16 +1528,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>0</v>
@@ -1556,16 +1563,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>0</v>
@@ -1591,16 +1598,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>1</v>
@@ -1626,16 +1633,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>1</v>
@@ -1661,16 +1668,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>0</v>
@@ -1696,16 +1703,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>0</v>
@@ -1756,162 +1763,162 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="D2" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="E2" s="0" t="s">
         <v>168</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="C3" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>167</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="E3" s="0" t="s">
         <v>172</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>171</v>
-      </c>
       <c r="C4" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="E4" s="0" t="s">
         <v>175</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>178</v>
-      </c>
       <c r="C5" s="0" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>178</v>
-      </c>
       <c r="C6" s="0" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>180</v>
-      </c>
       <c r="C7" s="0" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="C8" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>181</v>
-      </c>
       <c r="E8" s="0" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="0" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="E10" s="0" t="s">
         <v>182</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="0" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -1930,7 +1937,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1942,19 +1949,68 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>184</v>
       </c>
+      <c r="C2" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>138</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2214,17 +2270,15 @@
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>5.217773</v>
@@ -2260,100 +2314,100 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -2382,24 +2436,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>14</v>
@@ -2411,12 +2465,12 @@
         <v>6</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>5</v>
@@ -2460,45 +2514,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C2" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>1</v>
@@ -2516,24 +2570,24 @@
         <v>18</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B3" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C3" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G3" s="0" t="n">
         <v>6</v>
@@ -2545,18 +2599,18 @@
         <v>14</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C4" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>3</v>
@@ -2574,18 +2628,18 @@
         <v>14</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C5" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>4</v>
@@ -2603,24 +2657,24 @@
         <v>12</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C6" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G6" s="0" t="n">
         <v>6</v>
@@ -2632,18 +2686,18 @@
         <v>10</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C7" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>6</v>
@@ -2661,18 +2715,18 @@
         <v>8</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C8" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>7</v>
@@ -2690,18 +2744,18 @@
         <v>8</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C9" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>1</v>
@@ -2719,18 +2773,18 @@
         <v>16</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C10" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>2</v>
@@ -2748,18 +2802,18 @@
         <v>16</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C11" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>3</v>
@@ -2777,18 +2831,18 @@
         <v>14</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C12" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>4</v>
@@ -2806,18 +2860,18 @@
         <v>12</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C13" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>5</v>
@@ -2835,18 +2889,18 @@
         <v>12</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C14" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>6</v>
@@ -2864,18 +2918,18 @@
         <v>8</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C15" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>7</v>
@@ -2893,18 +2947,18 @@
         <v>6</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>1</v>
@@ -2922,18 +2976,18 @@
         <v>6</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>2</v>
@@ -2951,18 +3005,18 @@
         <v>4</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>3</v>
@@ -2980,18 +3034,18 @@
         <v>4</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>4</v>
@@ -3009,18 +3063,18 @@
         <v>2</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>1</v>
@@ -3038,18 +3092,18 @@
         <v>6</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>2</v>
@@ -3067,24 +3121,24 @@
         <v>6</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G22" s="0" t="n">
         <v>2</v>
@@ -3096,18 +3150,18 @@
         <v>2</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>4</v>
@@ -3125,15 +3179,15 @@
         <v>2</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>1</v>
@@ -3142,7 +3196,7 @@
         <v>42</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G24" s="0" t="n">
         <v>4</v>
@@ -3156,10 +3210,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>2</v>
@@ -3168,7 +3222,7 @@
         <v>45</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G25" s="0" t="n">
         <v>4</v>
@@ -3182,10 +3236,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>3</v>
@@ -3194,7 +3248,7 @@
         <v>48</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G26" s="0" t="n">
         <v>4</v>
@@ -3208,10 +3262,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>4</v>
@@ -3220,7 +3274,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G27" s="0" t="n">
         <v>4</v>
@@ -3234,10 +3288,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>5</v>
@@ -3246,7 +3300,7 @@
         <v>52</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G28" s="0" t="n">
         <v>4</v>
@@ -3286,30 +3340,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>9</v>
@@ -3318,7 +3372,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F2" s="0" t="s">
         <v>9</v>
@@ -3326,10 +3380,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>13</v>
@@ -3338,7 +3392,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>13</v>
@@ -3346,10 +3400,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>9</v>
@@ -3358,7 +3412,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F4" s="0" t="s">
         <v>9</v>
@@ -3390,68 +3444,68 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>73</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -3487,51 +3541,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="0" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="C2" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="D2" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="E2" s="0" t="s">
         <v>134</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>135</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>8</v>
@@ -3543,10 +3597,10 @@
         <v>7</v>
       </c>
       <c r="I2" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/PIMTC_GoogleSheets_Import.xlsx
+++ b/PIMTC_GoogleSheets_Import.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="203">
   <si>
     <t xml:space="preserve">rank</t>
   </si>
@@ -230,6 +230,9 @@
     <t xml:space="preserve">PIM Tennis Club is a community-based sports club located in Pupuk Iskandar Muda. We host regular training sessions, tournaments, and represent our organization in external events. Whether you're new to the sport or looking to sharpen your game, our club welcomes players of all levels.</t>
   </si>
   <si>
+    <t xml:space="preserve">https://osaftari-source.github.io/PIMTC/media/RPsPPb0.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.instagram.com/pimtennisclub/</t>
   </si>
   <si>
@@ -461,16 +464,46 @@
     <t xml:space="preserve">url</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-01</t>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First results are in from Group A: Osman/Ferdi with a 7-3 win over Dian/Fathur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1st match on Group A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osaftari-source.github.io/PIMTC/media/GtjaBpC.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First results are in from Group B: Fariz/Dian opened with a 7-3 win over Memed/Heri.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1st match on Group B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osaftari-source.github.io/PIMTC/media/Q3zga5E.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-20</t>
   </si>
   <si>
     <t xml:space="preserve">Group Stage Draw</t>
   </si>
   <si>
-    <t xml:space="preserve">Random pairs draw complete — 8 pairs split into Group A and Group B for round-robin group play. First results are in from Group B: Fariz/Dian opened with a 7-3 win over Memed/Heri.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text</t>
+    <t xml:space="preserve">Random pairs draw complete — 8 pairs split into Group A and Group B for round-robin group play.</t>
   </si>
   <si>
     <t xml:space="preserve">pair</t>
@@ -488,18 +521,15 @@
     <t xml:space="preserve">diff</t>
   </si>
   <si>
-    <t xml:space="preserve">Group Stage</t>
+    <t xml:space="preserve">Osman / Ferdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fatur / Dian</t>
   </si>
   <si>
     <t xml:space="preserve">Gipa / Mursal</t>
   </si>
   <si>
-    <t xml:space="preserve">Fatur / Dian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Osman / Ferdy</t>
-  </si>
-  <si>
     <t xml:space="preserve">Arief / Moeda</t>
   </si>
   <si>
@@ -518,6 +548,9 @@
     <t xml:space="preserve">day</t>
   </si>
   <si>
+    <t xml:space="preserve">time</t>
+  </si>
+  <si>
     <t xml:space="preserve">court</t>
   </si>
   <si>
@@ -533,6 +566,9 @@
     <t xml:space="preserve">Kamis</t>
   </si>
   <si>
+    <t xml:space="preserve">17:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lapangan 1</t>
   </si>
   <si>
@@ -563,6 +599,15 @@
     <t xml:space="preserve">Osman/Ferdy</t>
   </si>
   <si>
+    <t xml:space="preserve">20:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zes/Rahmat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heri/Memed</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-07-07</t>
   </si>
   <si>
@@ -575,25 +620,28 @@
     <t xml:space="preserve">Rabu</t>
   </si>
   <si>
-    <t xml:space="preserve">Heri/Memed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zes/Rahmat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Syahrul/Akbar</t>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
   </si>
   <si>
     <t xml:space="preserve">event</t>
   </si>
   <si>
-    <t xml:space="preserve">Club Highlights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIMTC on the court.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.instagram.com/reel/DGKAtoVh2eO/?igsh=MXFhZWY2dmlpaXJqcQ==</t>
+    <t xml:space="preserve">The Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://osaftari-source.github.io/PIMTC/media/ZddSRle.jpg</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1394,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -1359,39 +1407,113 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B2" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>150</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>145</v>
+      <c r="C6" s="0" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1423,121 +1545,121 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="0" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="E4" s="0" t="n">
         <v>0</v>
@@ -1563,16 +1685,16 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>4</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E5" s="0" t="n">
         <v>0</v>
@@ -1598,16 +1720,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E6" s="0" t="n">
         <v>1</v>
@@ -1633,16 +1755,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="E7" s="0" t="n">
         <v>1</v>
@@ -1668,16 +1790,16 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>3</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E8" s="0" t="n">
         <v>0</v>
@@ -1703,16 +1825,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>4</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E9" s="0" t="n">
         <v>0</v>
@@ -1752,173 +1874,276 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>163</v>
+        <v>173</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>168</v>
+        <v>179</v>
+      </c>
+      <c r="F2" s="0" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>172</v>
+        <v>183</v>
+      </c>
+      <c r="F3" s="0" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>175</v>
+        <v>186</v>
+      </c>
+      <c r="F4" s="0" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>172</v>
+        <v>189</v>
+      </c>
+      <c r="F5" s="0" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="C6" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>173</v>
-      </c>
       <c r="D6" s="0" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>175</v>
+        <v>186</v>
+      </c>
+      <c r="F6" s="0" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>174</v>
+        <v>183</v>
+      </c>
+      <c r="F7" s="0" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="E8" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="E11" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>180</v>
+      <c r="F11" s="0" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="0" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>198</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1937,7 +2162,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1949,33 +2174,41 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>186</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2004,13 +2237,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2270,15 +2503,17 @@
       <c r="C2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>5.217773</v>
@@ -2314,100 +2549,100 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2436,24 +2671,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>14</v>
@@ -2465,12 +2700,12 @@
         <v>6</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>5</v>
@@ -2514,45 +2749,45 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D2" s="0" t="n">
         <v>1</v>
@@ -2570,24 +2805,24 @@
         <v>18</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G3" s="0" t="n">
         <v>6</v>
@@ -2599,18 +2834,18 @@
         <v>14</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D4" s="0" t="n">
         <v>3</v>
@@ -2628,18 +2863,18 @@
         <v>14</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D5" s="0" t="n">
         <v>4</v>
@@ -2657,24 +2892,24 @@
         <v>12</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>5</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G6" s="0" t="n">
         <v>6</v>
@@ -2686,18 +2921,18 @@
         <v>10</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>6</v>
@@ -2715,18 +2950,18 @@
         <v>8</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" s="0" t="n">
         <v>7</v>
@@ -2744,18 +2979,18 @@
         <v>8</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" s="0" t="n">
         <v>1</v>
@@ -2773,18 +3008,18 @@
         <v>16</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>2</v>
@@ -2802,18 +3037,18 @@
         <v>16</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D11" s="0" t="n">
         <v>3</v>
@@ -2831,18 +3066,18 @@
         <v>14</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="0" t="n">
         <v>4</v>
@@ -2860,18 +3095,18 @@
         <v>12</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D13" s="0" t="n">
         <v>5</v>
@@ -2889,18 +3124,18 @@
         <v>12</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>6</v>
@@ -2918,18 +3153,18 @@
         <v>8</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D15" s="0" t="n">
         <v>7</v>
@@ -2947,18 +3182,18 @@
         <v>6</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" s="0" t="n">
         <v>1</v>
@@ -2976,18 +3211,18 @@
         <v>6</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" s="0" t="n">
         <v>2</v>
@@ -3005,18 +3240,18 @@
         <v>4</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D18" s="0" t="n">
         <v>3</v>
@@ -3034,18 +3269,18 @@
         <v>4</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" s="0" t="n">
         <v>4</v>
@@ -3063,18 +3298,18 @@
         <v>2</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D20" s="0" t="n">
         <v>1</v>
@@ -3092,18 +3327,18 @@
         <v>6</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D21" s="0" t="n">
         <v>2</v>
@@ -3121,24 +3356,24 @@
         <v>6</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D22" s="0" t="n">
         <v>3</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G22" s="0" t="n">
         <v>2</v>
@@ -3150,18 +3385,18 @@
         <v>2</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D23" s="0" t="n">
         <v>4</v>
@@ -3179,15 +3414,15 @@
         <v>2</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D24" s="0" t="n">
         <v>1</v>
@@ -3196,7 +3431,7 @@
         <v>42</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G24" s="0" t="n">
         <v>4</v>
@@ -3210,10 +3445,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D25" s="0" t="n">
         <v>2</v>
@@ -3222,7 +3457,7 @@
         <v>45</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G25" s="0" t="n">
         <v>4</v>
@@ -3236,10 +3471,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D26" s="0" t="n">
         <v>3</v>
@@ -3248,7 +3483,7 @@
         <v>48</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G26" s="0" t="n">
         <v>4</v>
@@ -3262,10 +3497,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D27" s="0" t="n">
         <v>4</v>
@@ -3274,7 +3509,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G27" s="0" t="n">
         <v>4</v>
@@ -3288,10 +3523,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D28" s="0" t="n">
         <v>5</v>
@@ -3300,7 +3535,7 @@
         <v>52</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G28" s="0" t="n">
         <v>4</v>
@@ -3340,30 +3575,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>9</v>
@@ -3372,7 +3607,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F2" s="0" t="s">
         <v>9</v>
@@ -3380,10 +3615,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>13</v>
@@ -3392,7 +3627,7 @@
         <v>17</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F3" s="0" t="s">
         <v>13</v>
@@ -3400,10 +3635,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>9</v>
@@ -3412,7 +3647,7 @@
         <v>13</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F4" s="0" t="s">
         <v>9</v>
@@ -3444,68 +3679,68 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -3541,51 +3776,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F2" s="0" t="n">
         <v>8</v>
@@ -3597,10 +3832,10 @@
         <v>7</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
